--- a/data/trans_dic/IP16A98-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 26,81</t>
+          <t>7,55; 26,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 28,85</t>
+          <t>6,91; 30,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 45,47</t>
+          <t>11,7; 45,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 23,17</t>
+          <t>3,66; 22,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 31,73</t>
+          <t>5,25; 29,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 26,05</t>
+          <t>5,83; 26,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 21,38</t>
+          <t>8,07; 21,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,77; 23,85</t>
+          <t>7,88; 24,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 28,34</t>
+          <t>9,75; 29,41</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 17,74</t>
+          <t>4,72; 17,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,02; 29,86</t>
+          <t>10,27; 31,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,81; 24,59</t>
+          <t>7,2; 24,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 21,12</t>
+          <t>7,44; 20,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,21; 28,63</t>
+          <t>9,75; 28,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 30,46</t>
+          <t>10,68; 31,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,95; 17,04</t>
+          <t>7,38; 16,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,91; 25,35</t>
+          <t>11,9; 26,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,77; 24,55</t>
+          <t>10,61; 24,71</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 30,15</t>
+          <t>6,9; 30,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 27,83</t>
+          <t>7,3; 28,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,63; 35,88</t>
+          <t>13,71; 37,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 35,1</t>
+          <t>7,94; 35,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 38,39</t>
+          <t>14,67; 40,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,74; 25,11</t>
+          <t>5,83; 23,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 27,59</t>
+          <t>10,87; 28,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 28,74</t>
+          <t>13,03; 28,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 25,59</t>
+          <t>11,03; 26,1</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 19,68</t>
+          <t>2,25; 17,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 33,48</t>
+          <t>8,36; 35,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 36,81</t>
+          <t>5,39; 39,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,43; 38,61</t>
+          <t>10,77; 40,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 42,79</t>
+          <t>11,85; 39,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 40,66</t>
+          <t>13,37; 40,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 23,53</t>
+          <t>7,68; 23,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 32,59</t>
+          <t>12,7; 33,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,39; 32,54</t>
+          <t>9,83; 33,01</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,92</t>
+          <t>8,11; 16,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,82</t>
+          <t>12,32; 23,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 27,41</t>
+          <t>11,06; 28,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 20,32</t>
+          <t>10,71; 20,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 26,83</t>
+          <t>14,86; 27,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 25,16</t>
+          <t>13,53; 25,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,31</t>
+          <t>10,81; 17,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,93; 22,79</t>
+          <t>14,85; 22,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,66; 24,32</t>
+          <t>13,02; 23,65</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5450</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4328</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3883</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9755</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>7649</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6833</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2702; 9563</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1867; 8195</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1869; 7275</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1383; 8527</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1258; 6974</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1304; 5948</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5938; 15579</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4019; 12683</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>3740; 11275</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5293</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7828</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6768</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7638</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9255</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>13693</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>15465</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>16022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2504; 9391</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4339; 13155</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3355; 11511</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4861; 13613</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4204; 12125</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5232; 15251</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8740; 19915</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10152; 22566</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>10147; 23625</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4875</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5587</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8576</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>14109</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14521</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2060; 9122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2636; 10469</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5094; 13913</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2154; 9694</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4908; 13462</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2693; 11000</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6197; 16218</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>9065; 19827</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>9186; 21746</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3925</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13517</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15365</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7199</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9489</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28882</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>582; 4611</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1846; 7747</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4199; 30966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2613; 9824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2696; 9083</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8649; 26205</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3854; 11894</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5692; 14861</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>14020; 47093</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21668</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32743</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33516</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40948</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>46712</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>66259</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11723; 24369</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15703; 29345</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19656; 49918</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16546; 31573</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18317; 33834</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24660; 45555</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32332; 51727</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>37240; 56783</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>46865; 85107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A98-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,72</t>
+          <t>7,48; 27,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 30,31</t>
+          <t>6,77; 28,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 45,52</t>
+          <t>11,13; 46,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 22,56</t>
+          <t>5,2; 24,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 29,09</t>
+          <t>4,86; 26,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 26,61</t>
+          <t>4,59; 25,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 21,17</t>
+          <t>7,72; 20,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 24,86</t>
+          <t>8,5; 23,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 29,41</t>
+          <t>9,61; 28,04</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 17,71</t>
+          <t>4,82; 17,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 31,14</t>
+          <t>10,14; 30,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 24,69</t>
+          <t>7,02; 24,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 20,83</t>
+          <t>7,44; 21,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 28,13</t>
+          <t>9,61; 29,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,68; 31,13</t>
+          <t>11,21; 31,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 16,82</t>
+          <t>7,4; 16,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,9; 26,44</t>
+          <t>11,97; 25,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 24,71</t>
+          <t>11,28; 24,54</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,9; 30,54</t>
+          <t>7,23; 30,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 28,98</t>
+          <t>6,74; 27,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 37,45</t>
+          <t>12,78; 36,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 35,72</t>
+          <t>8,17; 34,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 40,25</t>
+          <t>13,59; 37,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 23,83</t>
+          <t>5,35; 25,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,87; 28,45</t>
+          <t>10,32; 27,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,03; 28,5</t>
+          <t>13,65; 29,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 26,1</t>
+          <t>11,41; 25,28</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 17,79</t>
+          <t>2,25; 19,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,36; 35,11</t>
+          <t>8,0; 35,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 39,72</t>
+          <t>4,91; 38,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 40,49</t>
+          <t>11,04; 38,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 39,91</t>
+          <t>12,35; 43,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,37; 40,51</t>
+          <t>13,5; 41,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,68; 23,7</t>
+          <t>7,71; 23,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 33,15</t>
+          <t>12,66; 33,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 33,01</t>
+          <t>9,74; 32,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,85</t>
+          <t>8,16; 17,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,02</t>
+          <t>11,96; 23,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 28,09</t>
+          <t>11,04; 27,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,43</t>
+          <t>10,67; 20,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,86; 27,45</t>
+          <t>15,43; 27,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,0</t>
+          <t>13,15; 25,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 17,29</t>
+          <t>10,55; 17,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,65</t>
+          <t>15,13; 23,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 23,65</t>
+          <t>13,77; 23,99</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2702; 9563</t>
+          <t>2677; 9699</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1867; 8195</t>
+          <t>1831; 7737</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1869; 7275</t>
+          <t>1779; 7407</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1383; 8527</t>
+          <t>1965; 9236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1258; 6974</t>
+          <t>1164; 6434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1304; 5948</t>
+          <t>1026; 5714</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5938; 15579</t>
+          <t>5680; 15122</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4019; 12683</t>
+          <t>4334; 12208</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3740; 11275</t>
+          <t>3684; 10749</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2504; 9391</t>
+          <t>2554; 9495</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4339; 13155</t>
+          <t>4284; 13045</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3355; 11511</t>
+          <t>3271; 11499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4861; 13613</t>
+          <t>4863; 14089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4204; 12125</t>
+          <t>4143; 12569</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5232; 15251</t>
+          <t>5493; 15235</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8740; 19915</t>
+          <t>8763; 20002</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10152; 22566</t>
+          <t>10213; 21675</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10147; 23625</t>
+          <t>10785; 23458</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2060; 9122</t>
+          <t>2159; 9088</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2636; 10469</t>
+          <t>2435; 9808</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5094; 13913</t>
+          <t>4748; 13409</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2154; 9694</t>
+          <t>2218; 9478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4908; 13462</t>
+          <t>4545; 12620</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2693; 11000</t>
+          <t>2472; 11629</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6197; 16218</t>
+          <t>5881; 15865</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9065; 19827</t>
+          <t>9498; 20745</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9186; 21746</t>
+          <t>9505; 21060</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>582; 4611</t>
+          <t>583; 5054</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1846; 7747</t>
+          <t>1765; 7766</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4199; 30966</t>
+          <t>3831; 29901</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2613; 9824</t>
+          <t>2679; 9344</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2696; 9083</t>
+          <t>2811; 9806</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8649; 26205</t>
+          <t>8732; 26541</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3854; 11894</t>
+          <t>3870; 11798</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5692; 14861</t>
+          <t>5672; 15128</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14020; 47093</t>
+          <t>13900; 45978</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11723; 24369</t>
+          <t>11808; 24872</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15703; 29345</t>
+          <t>15240; 29441</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19656; 49918</t>
+          <t>19615; 49092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16546; 31573</t>
+          <t>16488; 31501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18317; 33834</t>
+          <t>19022; 33523</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24660; 45555</t>
+          <t>23963; 46435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32332; 51727</t>
+          <t>31577; 51700</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37240; 56783</t>
+          <t>37927; 58056</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46865; 85107</t>
+          <t>49549; 86352</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A98-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15,23%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>16,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24,29%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 27,1</t>
+          <t>4,17; 23,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 28,62</t>
+          <t>5,17; 31,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,13; 46,34</t>
+          <t>6,15; 29,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 24,43</t>
+          <t>7,32; 26,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 26,84</t>
+          <t>6,86; 28,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 25,56</t>
+          <t>10,38; 45,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,72; 20,55</t>
+          <t>7,41; 21,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 23,93</t>
+          <t>7,77; 23,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 28,04</t>
+          <t>10,53; 30,24</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,27%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 17,9</t>
+          <t>7,42; 21,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 30,88</t>
+          <t>9,21; 28,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 24,66</t>
+          <t>9,8; 29,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 21,56</t>
+          <t>3,84; 17,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 29,16</t>
+          <t>10,02; 29,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 31,1</t>
+          <t>8,4; 28,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 16,89</t>
+          <t>6,95; 17,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 25,4</t>
+          <t>11,91; 25,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,28; 24,54</t>
+          <t>11,9; 26,69</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25,48%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,61%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>16,32%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>15,47%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23,08%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25,48%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 30,43</t>
+          <t>8,48; 35,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 27,15</t>
+          <t>14,64; 38,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,78; 36,09</t>
+          <t>5,7; 25,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 34,92</t>
+          <t>6,92; 30,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,59; 37,73</t>
+          <t>7,32; 27,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,35; 25,19</t>
+          <t>12,69; 36,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,32; 27,83</t>
+          <t>10,71; 27,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,65; 29,82</t>
+          <t>12,54; 28,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 25,28</t>
+          <t>10,65; 25,58</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24,45%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>17,79%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 19,5</t>
+          <t>10,43; 38,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 35,19</t>
+          <t>12,35; 42,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 38,36</t>
+          <t>13,69; 41,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 38,51</t>
+          <t>2,24; 19,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 43,09</t>
+          <t>6,47; 33,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 41,03</t>
+          <t>10,1; 28,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 23,51</t>
+          <t>7,54; 23,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 33,75</t>
+          <t>12,3; 32,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,74; 32,23</t>
+          <t>13,84; 31,29</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,2</t>
+          <t>10,93; 20,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 23,1</t>
+          <t>14,75; 26,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 27,62</t>
+          <t>13,24; 25,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,38</t>
+          <t>8,16; 16,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,19</t>
+          <t>11,59; 22,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,15; 25,49</t>
+          <t>14,25; 24,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,28</t>
+          <t>10,65; 17,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,13; 23,15</t>
+          <t>14,93; 22,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,99</t>
+          <t>15,03; 23,36</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3321</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>5450</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>4328</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3883</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4304</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>5985</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2677; 9699</t>
+          <t>1574; 8760</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1831; 7737</t>
+          <t>1239; 7607</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1779; 7407</t>
+          <t>1072; 5084</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1965; 9236</t>
+          <t>2620; 9594</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1164; 6434</t>
+          <t>1854; 7799</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1026; 5714</t>
+          <t>1471; 6465</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5680; 15122</t>
+          <t>5454; 15734</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4334; 12208</t>
+          <t>3965; 12166</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3684; 10749</t>
+          <t>3327; 9557</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7638</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7532</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5293</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>7828</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6768</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7638</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>14544</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2554; 9495</t>
+          <t>4847; 13806</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4284; 13045</t>
+          <t>3970; 12337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3271; 11499</t>
+          <t>4040; 12225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4863; 14089</t>
+          <t>2038; 9408</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4143; 12569</t>
+          <t>4233; 12612</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5493; 15235</t>
+          <t>3437; 11602</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8763; 20002</t>
+          <t>8231; 20172</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10213; 21675</t>
+          <t>10163; 21631</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10785; 23458</t>
+          <t>9773; 21923</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>5427</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8521</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5545</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>4875</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>5587</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8576</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5427</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>8521</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>8702</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14521</t>
+          <t>14247</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2159; 9088</t>
+          <t>2301; 9526</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2435; 9808</t>
+          <t>4898; 12839</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4748; 13409</t>
+          <t>2508; 11000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2218; 9478</t>
+          <t>2066; 9005</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4545; 12620</t>
+          <t>2643; 10055</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2472; 11629</t>
+          <t>4815; 13756</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5881; 15865</t>
+          <t>6107; 15725</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9498; 20745</t>
+          <t>8721; 19996</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9505; 21060</t>
+          <t>8721; 20958</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5565</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14675</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1854</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3925</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13517</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5344</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5565</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>28882</t>
+          <t>23328</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>583; 5054</t>
+          <t>2530; 9368</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1765; 7766</t>
+          <t>2810; 9738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3831; 29901</t>
+          <t>8529; 26034</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2679; 9344</t>
+          <t>581; 5101</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2811; 9806</t>
+          <t>1427; 7387</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8732; 26541</t>
+          <t>5048; 14443</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3870; 11798</t>
+          <t>3782; 11807</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5672; 15128</t>
+          <t>5513; 14610</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13900; 45978</t>
+          <t>15544; 35140</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11808; 24872</t>
+          <t>16896; 31398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15240; 29441</t>
+          <t>18186; 33081</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19615; 49092</t>
+          <t>21832; 42758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16488; 31501</t>
+          <t>11807; 24464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19022; 33523</t>
+          <t>14773; 29092</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23963; 46435</t>
+          <t>20372; 35456</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31577; 51700</t>
+          <t>31850; 51779</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37927; 58056</t>
+          <t>37429; 57146</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49549; 86352</t>
+          <t>46288; 71920</t>
         </is>
       </c>
     </row>
